--- a/artfynd/A 53122-2024 artfynd.xlsx
+++ b/artfynd/A 53122-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747606</v>
+        <v>122747619</v>
       </c>
       <c r="B2" t="n">
-        <v>90340</v>
+        <v>89991</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>256703</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758247</v>
+        <v>758431</v>
       </c>
       <c r="R2" t="n">
-        <v>7226119</v>
+        <v>7226257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747624</v>
+        <v>122747638</v>
       </c>
       <c r="B3" t="n">
-        <v>92112</v>
+        <v>91694</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Gökberget V, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758400</v>
+        <v>758363</v>
       </c>
       <c r="R3" t="n">
-        <v>7226209</v>
+        <v>7226141</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747641</v>
+        <v>122747635</v>
       </c>
       <c r="B4" t="n">
-        <v>91591</v>
+        <v>92215</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1958</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758366</v>
+        <v>758363</v>
       </c>
       <c r="R4" t="n">
-        <v>7226139</v>
+        <v>7226170</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747642</v>
+        <v>122747639</v>
       </c>
       <c r="B5" t="n">
-        <v>90340</v>
+        <v>92221</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,34 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758356</v>
+        <v>758361</v>
       </c>
       <c r="R5" t="n">
-        <v>7226127</v>
+        <v>7226146</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747638</v>
+        <v>122747626</v>
       </c>
       <c r="B6" t="n">
-        <v>91591</v>
+        <v>97307</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1958</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gökberget V, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>758363</v>
+        <v>758357</v>
       </c>
       <c r="R6" t="n">
-        <v>7226141</v>
+        <v>7226191</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747614</v>
+        <v>122747630</v>
       </c>
       <c r="B7" t="n">
-        <v>92110</v>
+        <v>97307</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>758432</v>
+        <v>758356</v>
       </c>
       <c r="R7" t="n">
-        <v>7226289</v>
+        <v>7226177</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747604</v>
+        <v>122747606</v>
       </c>
       <c r="B8" t="n">
-        <v>90340</v>
+        <v>90443</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>758256</v>
+        <v>758247</v>
       </c>
       <c r="R8" t="n">
-        <v>7226053</v>
+        <v>7226119</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747639</v>
+        <v>122747642</v>
       </c>
       <c r="B9" t="n">
-        <v>92118</v>
+        <v>90443</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,34 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>758361</v>
+        <v>758356</v>
       </c>
       <c r="R9" t="n">
-        <v>7226146</v>
+        <v>7226127</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747633</v>
+        <v>122747613</v>
       </c>
       <c r="B10" t="n">
-        <v>92118</v>
+        <v>92256</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,38 +1535,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>758361</v>
+        <v>758391</v>
       </c>
       <c r="R10" t="n">
-        <v>7226178</v>
+        <v>7226328</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747619</v>
+        <v>122747641</v>
       </c>
       <c r="B11" t="n">
-        <v>89888</v>
+        <v>91694</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>1958</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758431</v>
+        <v>758366</v>
       </c>
       <c r="R11" t="n">
-        <v>7226257</v>
+        <v>7226139</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122747626</v>
+        <v>122747633</v>
       </c>
       <c r="B12" t="n">
-        <v>97204</v>
+        <v>92221</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>758357</v>
+        <v>758361</v>
       </c>
       <c r="R12" t="n">
-        <v>7226191</v>
+        <v>7226178</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122747613</v>
+        <v>122747629</v>
       </c>
       <c r="B13" t="n">
-        <v>92153</v>
+        <v>92215</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,34 +1857,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>758391</v>
+        <v>758350</v>
       </c>
       <c r="R13" t="n">
-        <v>7226328</v>
+        <v>7226181</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122747629</v>
+        <v>122747604</v>
       </c>
       <c r="B14" t="n">
-        <v>92112</v>
+        <v>90443</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,38 +1959,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>758350</v>
+        <v>758256</v>
       </c>
       <c r="R14" t="n">
-        <v>7226181</v>
+        <v>7226053</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122747635</v>
+        <v>122747624</v>
       </c>
       <c r="B15" t="n">
-        <v>92112</v>
+        <v>92215</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2089,14 +2089,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>758363</v>
+        <v>758400</v>
       </c>
       <c r="R15" t="n">
-        <v>7226170</v>
+        <v>7226209</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747630</v>
+        <v>122747611</v>
       </c>
       <c r="B16" t="n">
-        <v>97204</v>
+        <v>92213</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,38 +2171,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>758356</v>
+        <v>758277</v>
       </c>
       <c r="R16" t="n">
-        <v>7226177</v>
+        <v>7226119</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
         <v>122747609</v>
       </c>
       <c r="B17" t="n">
-        <v>89888</v>
+        <v>89991</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122747611</v>
+        <v>122747614</v>
       </c>
       <c r="B18" t="n">
-        <v>92110</v>
+        <v>92213</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,14 +2407,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>758277</v>
+        <v>758432</v>
       </c>
       <c r="R18" t="n">
-        <v>7226119</v>
+        <v>7226289</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 53122-2024 artfynd.xlsx
+++ b/artfynd/A 53122-2024 artfynd.xlsx
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747641</v>
+        <v>122747633</v>
       </c>
       <c r="B11" t="n">
-        <v>91694</v>
+        <v>92221</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758366</v>
+        <v>758361</v>
       </c>
       <c r="R11" t="n">
-        <v>7226139</v>
+        <v>7226178</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122747633</v>
+        <v>122747629</v>
       </c>
       <c r="B12" t="n">
-        <v>92221</v>
+        <v>92215</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,38 +1747,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>758361</v>
+        <v>758350</v>
       </c>
       <c r="R12" t="n">
-        <v>7226178</v>
+        <v>7226181</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122747629</v>
+        <v>122747641</v>
       </c>
       <c r="B13" t="n">
-        <v>92215</v>
+        <v>91694</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>758350</v>
+        <v>758366</v>
       </c>
       <c r="R13" t="n">
-        <v>7226181</v>
+        <v>7226139</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 53122-2024 artfynd.xlsx
+++ b/artfynd/A 53122-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747619</v>
+        <v>122747626</v>
       </c>
       <c r="B2" t="n">
-        <v>89991</v>
+        <v>97315</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758431</v>
+        <v>758357</v>
       </c>
       <c r="R2" t="n">
-        <v>7226257</v>
+        <v>7226191</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747638</v>
+        <v>122747635</v>
       </c>
       <c r="B3" t="n">
-        <v>91694</v>
+        <v>92219</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1958</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gökberget V, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>758363</v>
       </c>
       <c r="R3" t="n">
-        <v>7226141</v>
+        <v>7226170</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747635</v>
+        <v>122747633</v>
       </c>
       <c r="B4" t="n">
-        <v>92215</v>
+        <v>92225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758363</v>
+        <v>758361</v>
       </c>
       <c r="R4" t="n">
-        <v>7226170</v>
+        <v>7226178</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747639</v>
+        <v>122747638</v>
       </c>
       <c r="B5" t="n">
-        <v>92221</v>
+        <v>91698</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Gökberget V, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758361</v>
+        <v>758363</v>
       </c>
       <c r="R5" t="n">
-        <v>7226146</v>
+        <v>7226141</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747626</v>
+        <v>122747609</v>
       </c>
       <c r="B6" t="n">
-        <v>97307</v>
+        <v>89995</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet N, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>758357</v>
+        <v>758253</v>
       </c>
       <c r="R6" t="n">
-        <v>7226191</v>
+        <v>7226123</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747630</v>
+        <v>122747641</v>
       </c>
       <c r="B7" t="n">
-        <v>97307</v>
+        <v>91698</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>1958</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>758356</v>
+        <v>758366</v>
       </c>
       <c r="R7" t="n">
-        <v>7226177</v>
+        <v>7226139</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747606</v>
+        <v>122747629</v>
       </c>
       <c r="B8" t="n">
-        <v>90443</v>
+        <v>92219</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>256703</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>758247</v>
+        <v>758350</v>
       </c>
       <c r="R8" t="n">
-        <v>7226119</v>
+        <v>7226181</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747642</v>
+        <v>122747611</v>
       </c>
       <c r="B9" t="n">
-        <v>90443</v>
+        <v>92217</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,38 +1429,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>256703</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>758356</v>
+        <v>758277</v>
       </c>
       <c r="R9" t="n">
-        <v>7226127</v>
+        <v>7226119</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747613</v>
+        <v>122747614</v>
       </c>
       <c r="B10" t="n">
-        <v>92256</v>
+        <v>92217</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,34 +1539,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>758391</v>
+        <v>758432</v>
       </c>
       <c r="R10" t="n">
-        <v>7226328</v>
+        <v>7226289</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747633</v>
+        <v>122747630</v>
       </c>
       <c r="B11" t="n">
-        <v>92221</v>
+        <v>97315</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,34 +1645,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758361</v>
+        <v>758356</v>
       </c>
       <c r="R11" t="n">
-        <v>7226178</v>
+        <v>7226177</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122747629</v>
+        <v>122747604</v>
       </c>
       <c r="B12" t="n">
-        <v>92215</v>
+        <v>90447</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,38 +1747,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>758350</v>
+        <v>758256</v>
       </c>
       <c r="R12" t="n">
-        <v>7226181</v>
+        <v>7226053</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122747641</v>
+        <v>122747613</v>
       </c>
       <c r="B13" t="n">
-        <v>91694</v>
+        <v>92260</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,38 +1853,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1958</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>758366</v>
+        <v>758391</v>
       </c>
       <c r="R13" t="n">
-        <v>7226139</v>
+        <v>7226328</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122747604</v>
+        <v>122747619</v>
       </c>
       <c r="B14" t="n">
-        <v>90443</v>
+        <v>89995</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>256703</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>758256</v>
+        <v>758431</v>
       </c>
       <c r="R14" t="n">
-        <v>7226053</v>
+        <v>7226257</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122747624</v>
+        <v>122747606</v>
       </c>
       <c r="B15" t="n">
-        <v>92215</v>
+        <v>90447</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,38 +2065,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>758400</v>
+        <v>758247</v>
       </c>
       <c r="R15" t="n">
-        <v>7226209</v>
+        <v>7226119</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747611</v>
+        <v>122747642</v>
       </c>
       <c r="B16" t="n">
-        <v>92213</v>
+        <v>90447</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,38 +2171,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>256703</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>758277</v>
+        <v>758356</v>
       </c>
       <c r="R16" t="n">
-        <v>7226119</v>
+        <v>7226127</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747609</v>
+        <v>122747624</v>
       </c>
       <c r="B17" t="n">
-        <v>89991</v>
+        <v>92219</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,34 +2281,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åfallet N, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>758253</v>
+        <v>758400</v>
       </c>
       <c r="R17" t="n">
-        <v>7226123</v>
+        <v>7226209</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122747614</v>
+        <v>122747639</v>
       </c>
       <c r="B18" t="n">
-        <v>92213</v>
+        <v>92225</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,38 +2383,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>758432</v>
+        <v>758361</v>
       </c>
       <c r="R18" t="n">
-        <v>7226289</v>
+        <v>7226146</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 53122-2024 artfynd.xlsx
+++ b/artfynd/A 53122-2024 artfynd.xlsx
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122747613</v>
+        <v>122747619</v>
       </c>
       <c r="B13" t="n">
-        <v>92260</v>
+        <v>89995</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,34 +1857,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5966</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>758391</v>
+        <v>758431</v>
       </c>
       <c r="R13" t="n">
-        <v>7226328</v>
+        <v>7226257</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122747619</v>
+        <v>122747613</v>
       </c>
       <c r="B14" t="n">
-        <v>89995</v>
+        <v>92260</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,34 +1963,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>758431</v>
+        <v>758391</v>
       </c>
       <c r="R14" t="n">
-        <v>7226257</v>
+        <v>7226328</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122747606</v>
+        <v>122747624</v>
       </c>
       <c r="B15" t="n">
-        <v>90447</v>
+        <v>92219</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,38 +2065,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>256703</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>758247</v>
+        <v>758400</v>
       </c>
       <c r="R15" t="n">
-        <v>7226119</v>
+        <v>7226209</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747624</v>
+        <v>122747606</v>
       </c>
       <c r="B17" t="n">
-        <v>92219</v>
+        <v>90447</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,38 +2277,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>758400</v>
+        <v>758247</v>
       </c>
       <c r="R17" t="n">
-        <v>7226209</v>
+        <v>7226119</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 53122-2024 artfynd.xlsx
+++ b/artfynd/A 53122-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747626</v>
+        <v>122747641</v>
       </c>
       <c r="B2" t="n">
-        <v>97315</v>
+        <v>91698</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>1958</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758357</v>
+        <v>758366</v>
       </c>
       <c r="R2" t="n">
-        <v>7226191</v>
+        <v>7226139</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747635</v>
+        <v>122747624</v>
       </c>
       <c r="B3" t="n">
         <v>92219</v>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758363</v>
+        <v>758400</v>
       </c>
       <c r="R3" t="n">
-        <v>7226170</v>
+        <v>7226209</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747633</v>
+        <v>122747639</v>
       </c>
       <c r="B4" t="n">
         <v>92225</v>
@@ -923,14 +923,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>758361</v>
       </c>
       <c r="R4" t="n">
-        <v>7226178</v>
+        <v>7226146</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747638</v>
+        <v>122747642</v>
       </c>
       <c r="B5" t="n">
-        <v>91698</v>
+        <v>90447</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1958</v>
+        <v>256703</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gökberget V, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758363</v>
+        <v>758356</v>
       </c>
       <c r="R5" t="n">
-        <v>7226141</v>
+        <v>7226127</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747609</v>
+        <v>122747619</v>
       </c>
       <c r="B6" t="n">
         <v>89995</v>
@@ -1135,14 +1135,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åfallet N, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>758253</v>
+        <v>758431</v>
       </c>
       <c r="R6" t="n">
-        <v>7226123</v>
+        <v>7226257</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747641</v>
+        <v>122747609</v>
       </c>
       <c r="B7" t="n">
-        <v>91698</v>
+        <v>89995</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Åfallet N, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>758366</v>
+        <v>758253</v>
       </c>
       <c r="R7" t="n">
-        <v>7226139</v>
+        <v>7226123</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747611</v>
+        <v>122747633</v>
       </c>
       <c r="B9" t="n">
-        <v>92217</v>
+        <v>92225</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,38 +1429,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>758277</v>
+        <v>758361</v>
       </c>
       <c r="R9" t="n">
-        <v>7226119</v>
+        <v>7226178</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747614</v>
+        <v>122747626</v>
       </c>
       <c r="B10" t="n">
-        <v>92217</v>
+        <v>97315</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>758432</v>
+        <v>758357</v>
       </c>
       <c r="R10" t="n">
-        <v>7226289</v>
+        <v>7226191</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747630</v>
+        <v>122747604</v>
       </c>
       <c r="B11" t="n">
-        <v>97315</v>
+        <v>90447</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,34 +1645,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>256703</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758356</v>
+        <v>758256</v>
       </c>
       <c r="R11" t="n">
-        <v>7226177</v>
+        <v>7226053</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122747604</v>
+        <v>122747606</v>
       </c>
       <c r="B12" t="n">
         <v>90447</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>758256</v>
+        <v>758247</v>
       </c>
       <c r="R12" t="n">
-        <v>7226053</v>
+        <v>7226119</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122747619</v>
+        <v>122747638</v>
       </c>
       <c r="B13" t="n">
-        <v>89995</v>
+        <v>91698</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,38 +1853,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>1958</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Gökberget V, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>758431</v>
+        <v>758363</v>
       </c>
       <c r="R13" t="n">
-        <v>7226257</v>
+        <v>7226141</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122747613</v>
+        <v>122747614</v>
       </c>
       <c r="B14" t="n">
-        <v>92260</v>
+        <v>92217</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,34 +1963,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>758391</v>
+        <v>758432</v>
       </c>
       <c r="R14" t="n">
-        <v>7226328</v>
+        <v>7226289</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122747624</v>
+        <v>122747613</v>
       </c>
       <c r="B15" t="n">
-        <v>92219</v>
+        <v>92260</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,34 +2069,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>758400</v>
+        <v>758391</v>
       </c>
       <c r="R15" t="n">
-        <v>7226209</v>
+        <v>7226328</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747642</v>
+        <v>122747630</v>
       </c>
       <c r="B16" t="n">
-        <v>90447</v>
+        <v>97315</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,34 +2175,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>256703</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
         <v>758356</v>
       </c>
       <c r="R16" t="n">
-        <v>7226127</v>
+        <v>7226177</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747606</v>
+        <v>122747635</v>
       </c>
       <c r="B17" t="n">
-        <v>90447</v>
+        <v>92219</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,38 +2277,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>256703</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>758247</v>
+        <v>758363</v>
       </c>
       <c r="R17" t="n">
-        <v>7226119</v>
+        <v>7226170</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122747639</v>
+        <v>122747611</v>
       </c>
       <c r="B18" t="n">
-        <v>92225</v>
+        <v>92217</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,25 +2383,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2411,10 +2411,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>758361</v>
+        <v>758277</v>
       </c>
       <c r="R18" t="n">
-        <v>7226146</v>
+        <v>7226119</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 53122-2024 artfynd.xlsx
+++ b/artfynd/A 53122-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747641</v>
+        <v>122747629</v>
       </c>
       <c r="B2" t="n">
-        <v>91698</v>
+        <v>92219</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1958</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758366</v>
+        <v>758350</v>
       </c>
       <c r="R2" t="n">
-        <v>7226139</v>
+        <v>7226181</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747624</v>
+        <v>122747611</v>
       </c>
       <c r="B3" t="n">
-        <v>92219</v>
+        <v>92217</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758400</v>
+        <v>758277</v>
       </c>
       <c r="R3" t="n">
-        <v>7226209</v>
+        <v>7226119</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747639</v>
+        <v>122747642</v>
       </c>
       <c r="B4" t="n">
-        <v>92225</v>
+        <v>90447</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758361</v>
+        <v>758356</v>
       </c>
       <c r="R4" t="n">
-        <v>7226146</v>
+        <v>7226127</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747642</v>
+        <v>122747638</v>
       </c>
       <c r="B5" t="n">
-        <v>90447</v>
+        <v>91698</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>256703</v>
+        <v>1958</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Gökberget V, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758356</v>
+        <v>758363</v>
       </c>
       <c r="R5" t="n">
-        <v>7226127</v>
+        <v>7226141</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747619</v>
+        <v>122747641</v>
       </c>
       <c r="B6" t="n">
-        <v>89995</v>
+        <v>91698</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>1958</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>758431</v>
+        <v>758366</v>
       </c>
       <c r="R6" t="n">
-        <v>7226257</v>
+        <v>7226139</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747609</v>
+        <v>122747639</v>
       </c>
       <c r="B7" t="n">
-        <v>89995</v>
+        <v>92225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åfallet N, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>758253</v>
+        <v>758361</v>
       </c>
       <c r="R7" t="n">
-        <v>7226123</v>
+        <v>7226146</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747629</v>
+        <v>122747609</v>
       </c>
       <c r="B8" t="n">
-        <v>92219</v>
+        <v>89995</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,34 +1327,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Åfallet N, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>758350</v>
+        <v>758253</v>
       </c>
       <c r="R8" t="n">
-        <v>7226181</v>
+        <v>7226123</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747633</v>
+        <v>122747619</v>
       </c>
       <c r="B9" t="n">
-        <v>92225</v>
+        <v>89995</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,38 +1429,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>758361</v>
+        <v>758431</v>
       </c>
       <c r="R9" t="n">
-        <v>7226178</v>
+        <v>7226257</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747626</v>
+        <v>122747614</v>
       </c>
       <c r="B10" t="n">
-        <v>97315</v>
+        <v>92217</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>758357</v>
+        <v>758432</v>
       </c>
       <c r="R10" t="n">
-        <v>7226191</v>
+        <v>7226289</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747604</v>
+        <v>122747613</v>
       </c>
       <c r="B11" t="n">
-        <v>90447</v>
+        <v>92260</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>256703</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758256</v>
+        <v>758391</v>
       </c>
       <c r="R11" t="n">
-        <v>7226053</v>
+        <v>7226328</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122747606</v>
+        <v>122747604</v>
       </c>
       <c r="B12" t="n">
         <v>90447</v>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>758247</v>
+        <v>758256</v>
       </c>
       <c r="R12" t="n">
-        <v>7226119</v>
+        <v>7226053</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122747638</v>
+        <v>122747635</v>
       </c>
       <c r="B13" t="n">
-        <v>91698</v>
+        <v>92219</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,38 +1853,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1958</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gökberget V, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
         <v>758363</v>
       </c>
       <c r="R13" t="n">
-        <v>7226141</v>
+        <v>7226170</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122747614</v>
+        <v>122747606</v>
       </c>
       <c r="B14" t="n">
-        <v>92217</v>
+        <v>90447</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,38 +1959,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>256703</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>758432</v>
+        <v>758247</v>
       </c>
       <c r="R14" t="n">
-        <v>7226289</v>
+        <v>7226119</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122747613</v>
+        <v>122747633</v>
       </c>
       <c r="B15" t="n">
-        <v>92260</v>
+        <v>92225</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,38 +2065,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>758391</v>
+        <v>758361</v>
       </c>
       <c r="R15" t="n">
-        <v>7226328</v>
+        <v>7226178</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747630</v>
+        <v>122747624</v>
       </c>
       <c r="B16" t="n">
-        <v>97315</v>
+        <v>92219</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,38 +2171,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>758356</v>
+        <v>758400</v>
       </c>
       <c r="R16" t="n">
-        <v>7226177</v>
+        <v>7226209</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747635</v>
+        <v>122747626</v>
       </c>
       <c r="B17" t="n">
-        <v>92219</v>
+        <v>97317</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,38 +2277,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>758363</v>
+        <v>758357</v>
       </c>
       <c r="R17" t="n">
-        <v>7226170</v>
+        <v>7226191</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122747611</v>
+        <v>122747630</v>
       </c>
       <c r="B18" t="n">
-        <v>92217</v>
+        <v>97317</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,38 +2383,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>758277</v>
+        <v>758356</v>
       </c>
       <c r="R18" t="n">
-        <v>7226119</v>
+        <v>7226177</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 53122-2024 artfynd.xlsx
+++ b/artfynd/A 53122-2024 artfynd.xlsx
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747613</v>
+        <v>122747604</v>
       </c>
       <c r="B11" t="n">
-        <v>92260</v>
+        <v>90447</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>256703</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758391</v>
+        <v>758256</v>
       </c>
       <c r="R11" t="n">
-        <v>7226328</v>
+        <v>7226053</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122747604</v>
+        <v>122747613</v>
       </c>
       <c r="B12" t="n">
-        <v>90447</v>
+        <v>92260</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,38 +1747,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>256703</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>758256</v>
+        <v>758391</v>
       </c>
       <c r="R12" t="n">
-        <v>7226053</v>
+        <v>7226328</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 53122-2024 artfynd.xlsx
+++ b/artfynd/A 53122-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747629</v>
+        <v>122747641</v>
       </c>
       <c r="B2" t="n">
-        <v>92219</v>
+        <v>91698</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758350</v>
+        <v>758366</v>
       </c>
       <c r="R2" t="n">
-        <v>7226181</v>
+        <v>7226139</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747611</v>
+        <v>122747624</v>
       </c>
       <c r="B3" t="n">
-        <v>92217</v>
+        <v>92219</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758277</v>
+        <v>758400</v>
       </c>
       <c r="R3" t="n">
-        <v>7226119</v>
+        <v>7226209</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747642</v>
+        <v>122747639</v>
       </c>
       <c r="B4" t="n">
-        <v>90447</v>
+        <v>92225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758356</v>
+        <v>758361</v>
       </c>
       <c r="R4" t="n">
-        <v>7226127</v>
+        <v>7226146</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747641</v>
+        <v>122747619</v>
       </c>
       <c r="B6" t="n">
-        <v>91698</v>
+        <v>89995</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1958</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>758366</v>
+        <v>758431</v>
       </c>
       <c r="R6" t="n">
-        <v>7226139</v>
+        <v>7226257</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747639</v>
+        <v>122747613</v>
       </c>
       <c r="B7" t="n">
-        <v>92225</v>
+        <v>92260</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>758361</v>
+        <v>758391</v>
       </c>
       <c r="R7" t="n">
-        <v>7226146</v>
+        <v>7226328</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747609</v>
+        <v>122747635</v>
       </c>
       <c r="B8" t="n">
-        <v>89995</v>
+        <v>92219</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,34 +1327,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åfallet N, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>758253</v>
+        <v>758363</v>
       </c>
       <c r="R8" t="n">
-        <v>7226123</v>
+        <v>7226170</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747619</v>
+        <v>122747606</v>
       </c>
       <c r="B9" t="n">
-        <v>89995</v>
+        <v>90447</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,25 +1429,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1962</v>
+        <v>256703</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>758431</v>
+        <v>758247</v>
       </c>
       <c r="R9" t="n">
-        <v>7226257</v>
+        <v>7226119</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747614</v>
+        <v>122747633</v>
       </c>
       <c r="B10" t="n">
-        <v>92217</v>
+        <v>92225</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>758432</v>
+        <v>758361</v>
       </c>
       <c r="R10" t="n">
-        <v>7226289</v>
+        <v>7226178</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747604</v>
+        <v>122747626</v>
       </c>
       <c r="B11" t="n">
-        <v>90447</v>
+        <v>97317</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,34 +1645,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>256703</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758256</v>
+        <v>758357</v>
       </c>
       <c r="R11" t="n">
-        <v>7226053</v>
+        <v>7226191</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122747613</v>
+        <v>122747609</v>
       </c>
       <c r="B12" t="n">
-        <v>92260</v>
+        <v>89995</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,34 +1751,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Åfallet N, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>758391</v>
+        <v>758253</v>
       </c>
       <c r="R12" t="n">
-        <v>7226328</v>
+        <v>7226123</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122747635</v>
+        <v>122747611</v>
       </c>
       <c r="B13" t="n">
-        <v>92219</v>
+        <v>92217</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,21 +1857,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>758363</v>
+        <v>758277</v>
       </c>
       <c r="R13" t="n">
-        <v>7226170</v>
+        <v>7226119</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122747606</v>
+        <v>122747614</v>
       </c>
       <c r="B14" t="n">
-        <v>90447</v>
+        <v>92217</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,38 +1959,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>256703</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>758247</v>
+        <v>758432</v>
       </c>
       <c r="R14" t="n">
-        <v>7226119</v>
+        <v>7226289</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122747633</v>
+        <v>122747604</v>
       </c>
       <c r="B15" t="n">
-        <v>92225</v>
+        <v>90447</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,34 +2069,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>758361</v>
+        <v>758256</v>
       </c>
       <c r="R15" t="n">
-        <v>7226178</v>
+        <v>7226053</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747624</v>
+        <v>122747642</v>
       </c>
       <c r="B16" t="n">
-        <v>92219</v>
+        <v>90447</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,25 +2171,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>758400</v>
+        <v>758356</v>
       </c>
       <c r="R16" t="n">
-        <v>7226209</v>
+        <v>7226127</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747626</v>
+        <v>122747629</v>
       </c>
       <c r="B17" t="n">
-        <v>97317</v>
+        <v>92219</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,38 +2277,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>758357</v>
+        <v>758350</v>
       </c>
       <c r="R17" t="n">
-        <v>7226191</v>
+        <v>7226181</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 53122-2024 artfynd.xlsx
+++ b/artfynd/A 53122-2024 artfynd.xlsx
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747626</v>
+        <v>122747609</v>
       </c>
       <c r="B11" t="n">
-        <v>97317</v>
+        <v>89995</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet N, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758357</v>
+        <v>758253</v>
       </c>
       <c r="R11" t="n">
-        <v>7226191</v>
+        <v>7226123</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122747609</v>
+        <v>122747611</v>
       </c>
       <c r="B12" t="n">
-        <v>89995</v>
+        <v>92217</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,34 +1751,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åfallet N, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>758253</v>
+        <v>758277</v>
       </c>
       <c r="R12" t="n">
-        <v>7226123</v>
+        <v>7226119</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122747611</v>
+        <v>122747626</v>
       </c>
       <c r="B13" t="n">
-        <v>92217</v>
+        <v>97317</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,38 +1853,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>758277</v>
+        <v>758357</v>
       </c>
       <c r="R13" t="n">
-        <v>7226119</v>
+        <v>7226191</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 53122-2024 artfynd.xlsx
+++ b/artfynd/A 53122-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747641</v>
+        <v>122747633</v>
       </c>
       <c r="B2" t="n">
-        <v>91698</v>
+        <v>92233</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758366</v>
+        <v>758361</v>
       </c>
       <c r="R2" t="n">
-        <v>7226139</v>
+        <v>7226178</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747624</v>
+        <v>122747629</v>
       </c>
       <c r="B3" t="n">
-        <v>92219</v>
+        <v>92227</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758400</v>
+        <v>758350</v>
       </c>
       <c r="R3" t="n">
-        <v>7226209</v>
+        <v>7226181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747639</v>
+        <v>122747614</v>
       </c>
       <c r="B4" t="n">
         <v>92225</v>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758361</v>
+        <v>758432</v>
       </c>
       <c r="R4" t="n">
-        <v>7226146</v>
+        <v>7226289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747638</v>
+        <v>122747611</v>
       </c>
       <c r="B5" t="n">
-        <v>91698</v>
+        <v>92225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1958</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gökberget V, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758363</v>
+        <v>758277</v>
       </c>
       <c r="R5" t="n">
-        <v>7226141</v>
+        <v>7226119</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747619</v>
+        <v>122747635</v>
       </c>
       <c r="B6" t="n">
-        <v>89995</v>
+        <v>92227</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,34 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>758431</v>
+        <v>758363</v>
       </c>
       <c r="R6" t="n">
-        <v>7226257</v>
+        <v>7226170</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747613</v>
+        <v>122747604</v>
       </c>
       <c r="B7" t="n">
-        <v>92260</v>
+        <v>90455</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>256703</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>758391</v>
+        <v>758256</v>
       </c>
       <c r="R7" t="n">
-        <v>7226328</v>
+        <v>7226053</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747635</v>
+        <v>122747619</v>
       </c>
       <c r="B8" t="n">
-        <v>92219</v>
+        <v>89995</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,34 +1327,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>758363</v>
+        <v>758431</v>
       </c>
       <c r="R8" t="n">
-        <v>7226170</v>
+        <v>7226257</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,7 +1420,7 @@
         <v>122747606</v>
       </c>
       <c r="B9" t="n">
-        <v>90447</v>
+        <v>90455</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747633</v>
+        <v>122747641</v>
       </c>
       <c r="B10" t="n">
-        <v>92225</v>
+        <v>91706</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,38 +1535,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>758361</v>
+        <v>758366</v>
       </c>
       <c r="R10" t="n">
-        <v>7226178</v>
+        <v>7226139</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747609</v>
+        <v>122747624</v>
       </c>
       <c r="B11" t="n">
-        <v>89995</v>
+        <v>92227</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,34 +1645,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åfallet N, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758253</v>
+        <v>758400</v>
       </c>
       <c r="R11" t="n">
-        <v>7226123</v>
+        <v>7226209</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122747611</v>
+        <v>122747639</v>
       </c>
       <c r="B12" t="n">
-        <v>92217</v>
+        <v>92233</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,25 +1747,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>758277</v>
+        <v>758361</v>
       </c>
       <c r="R12" t="n">
-        <v>7226119</v>
+        <v>7226146</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
         <v>122747626</v>
       </c>
       <c r="B13" t="n">
-        <v>97317</v>
+        <v>97325</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122747614</v>
+        <v>122747613</v>
       </c>
       <c r="B14" t="n">
-        <v>92217</v>
+        <v>92268</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,34 +1963,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>758432</v>
+        <v>758391</v>
       </c>
       <c r="R14" t="n">
-        <v>7226289</v>
+        <v>7226328</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122747604</v>
+        <v>122747609</v>
       </c>
       <c r="B15" t="n">
-        <v>90447</v>
+        <v>89995</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,38 +2065,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>256703</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Åfallet N, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>758256</v>
+        <v>758253</v>
       </c>
       <c r="R15" t="n">
-        <v>7226053</v>
+        <v>7226123</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747642</v>
+        <v>122747630</v>
       </c>
       <c r="B16" t="n">
-        <v>90447</v>
+        <v>97325</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,34 +2175,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>256703</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
         <v>758356</v>
       </c>
       <c r="R16" t="n">
-        <v>7226127</v>
+        <v>7226177</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747629</v>
+        <v>122747638</v>
       </c>
       <c r="B17" t="n">
-        <v>92219</v>
+        <v>91706</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,38 +2277,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Gökberget V, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>758350</v>
+        <v>758363</v>
       </c>
       <c r="R17" t="n">
-        <v>7226181</v>
+        <v>7226141</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122747630</v>
+        <v>122747642</v>
       </c>
       <c r="B18" t="n">
-        <v>97317</v>
+        <v>90455</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,34 +2387,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>256703</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
         <v>758356</v>
       </c>
       <c r="R18" t="n">
-        <v>7226177</v>
+        <v>7226127</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 53122-2024 artfynd.xlsx
+++ b/artfynd/A 53122-2024 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747604</v>
+        <v>122747619</v>
       </c>
       <c r="B7" t="n">
-        <v>90455</v>
+        <v>89995</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>256703</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>758256</v>
+        <v>758431</v>
       </c>
       <c r="R7" t="n">
-        <v>7226053</v>
+        <v>7226257</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747619</v>
+        <v>122747604</v>
       </c>
       <c r="B8" t="n">
-        <v>89995</v>
+        <v>90455</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>256703</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>758431</v>
+        <v>758256</v>
       </c>
       <c r="R8" t="n">
-        <v>7226257</v>
+        <v>7226053</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747606</v>
+        <v>122747641</v>
       </c>
       <c r="B9" t="n">
-        <v>90455</v>
+        <v>91706</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,38 +1429,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>256703</v>
+        <v>1958</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>758247</v>
+        <v>758366</v>
       </c>
       <c r="R9" t="n">
-        <v>7226119</v>
+        <v>7226139</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747641</v>
+        <v>122747624</v>
       </c>
       <c r="B10" t="n">
-        <v>91706</v>
+        <v>92227</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,38 +1535,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1958</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>758366</v>
+        <v>758400</v>
       </c>
       <c r="R10" t="n">
-        <v>7226139</v>
+        <v>7226209</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747624</v>
+        <v>122747606</v>
       </c>
       <c r="B11" t="n">
-        <v>92227</v>
+        <v>90455</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758400</v>
+        <v>758247</v>
       </c>
       <c r="R11" t="n">
-        <v>7226209</v>
+        <v>7226119</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 53122-2024 artfynd.xlsx
+++ b/artfynd/A 53122-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747633</v>
+        <v>122747638</v>
       </c>
       <c r="B2" t="n">
-        <v>92233</v>
+        <v>91706</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Gökberget V, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758361</v>
+        <v>758363</v>
       </c>
       <c r="R2" t="n">
-        <v>7226178</v>
+        <v>7226141</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747629</v>
+        <v>122747613</v>
       </c>
       <c r="B3" t="n">
-        <v>92227</v>
+        <v>92268</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758350</v>
+        <v>758391</v>
       </c>
       <c r="R3" t="n">
-        <v>7226181</v>
+        <v>7226328</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747614</v>
+        <v>122747630</v>
       </c>
       <c r="B4" t="n">
-        <v>92225</v>
+        <v>97325</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758432</v>
+        <v>758356</v>
       </c>
       <c r="R4" t="n">
-        <v>7226289</v>
+        <v>7226177</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747635</v>
+        <v>122747633</v>
       </c>
       <c r="B6" t="n">
-        <v>92227</v>
+        <v>92233</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>758363</v>
+        <v>758361</v>
       </c>
       <c r="R6" t="n">
-        <v>7226170</v>
+        <v>7226178</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747619</v>
+        <v>122747642</v>
       </c>
       <c r="B7" t="n">
-        <v>89995</v>
+        <v>90455</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>256703</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>758431</v>
+        <v>758356</v>
       </c>
       <c r="R7" t="n">
-        <v>7226257</v>
+        <v>7226127</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747604</v>
+        <v>122747606</v>
       </c>
       <c r="B8" t="n">
         <v>90455</v>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>758256</v>
+        <v>758247</v>
       </c>
       <c r="R8" t="n">
-        <v>7226053</v>
+        <v>7226119</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747641</v>
+        <v>122747626</v>
       </c>
       <c r="B9" t="n">
-        <v>91706</v>
+        <v>97325</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,38 +1429,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1958</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>758366</v>
+        <v>758357</v>
       </c>
       <c r="R9" t="n">
-        <v>7226139</v>
+        <v>7226191</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747624</v>
+        <v>122747641</v>
       </c>
       <c r="B10" t="n">
-        <v>92227</v>
+        <v>91706</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,38 +1535,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>758400</v>
+        <v>758366</v>
       </c>
       <c r="R10" t="n">
-        <v>7226209</v>
+        <v>7226139</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747606</v>
+        <v>122747609</v>
       </c>
       <c r="B11" t="n">
-        <v>90455</v>
+        <v>89995</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>256703</v>
+        <v>1962</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Åfallet N, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758247</v>
+        <v>758253</v>
       </c>
       <c r="R11" t="n">
-        <v>7226119</v>
+        <v>7226123</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122747639</v>
+        <v>122747629</v>
       </c>
       <c r="B12" t="n">
-        <v>92233</v>
+        <v>92227</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,38 +1747,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>758361</v>
+        <v>758350</v>
       </c>
       <c r="R12" t="n">
-        <v>7226146</v>
+        <v>7226181</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122747626</v>
+        <v>122747624</v>
       </c>
       <c r="B13" t="n">
-        <v>97325</v>
+        <v>92227</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>758357</v>
+        <v>758400</v>
       </c>
       <c r="R13" t="n">
-        <v>7226191</v>
+        <v>7226209</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122747613</v>
+        <v>122747619</v>
       </c>
       <c r="B14" t="n">
-        <v>92268</v>
+        <v>89995</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,34 +1963,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5966</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>758391</v>
+        <v>758431</v>
       </c>
       <c r="R14" t="n">
-        <v>7226328</v>
+        <v>7226257</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122747609</v>
+        <v>122747614</v>
       </c>
       <c r="B15" t="n">
-        <v>89995</v>
+        <v>92225</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,34 +2069,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åfallet N, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>758253</v>
+        <v>758432</v>
       </c>
       <c r="R15" t="n">
-        <v>7226123</v>
+        <v>7226289</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747630</v>
+        <v>122747604</v>
       </c>
       <c r="B16" t="n">
-        <v>97325</v>
+        <v>90455</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2175,34 +2175,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>256703</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>758356</v>
+        <v>758256</v>
       </c>
       <c r="R16" t="n">
-        <v>7226177</v>
+        <v>7226053</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747638</v>
+        <v>122747635</v>
       </c>
       <c r="B17" t="n">
-        <v>91706</v>
+        <v>92227</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,38 +2277,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1958</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gökberget V, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
         <v>758363</v>
       </c>
       <c r="R17" t="n">
-        <v>7226141</v>
+        <v>7226170</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122747642</v>
+        <v>122747639</v>
       </c>
       <c r="B18" t="n">
-        <v>90455</v>
+        <v>92233</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,34 +2387,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>758356</v>
+        <v>758361</v>
       </c>
       <c r="R18" t="n">
-        <v>7226127</v>
+        <v>7226146</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 53122-2024 artfynd.xlsx
+++ b/artfynd/A 53122-2024 artfynd.xlsx
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747609</v>
+        <v>122747629</v>
       </c>
       <c r="B11" t="n">
-        <v>89995</v>
+        <v>92227</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,34 +1645,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åfallet N, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758253</v>
+        <v>758350</v>
       </c>
       <c r="R11" t="n">
-        <v>7226123</v>
+        <v>7226181</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122747629</v>
+        <v>122747609</v>
       </c>
       <c r="B12" t="n">
-        <v>92227</v>
+        <v>89995</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,34 +1751,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Åfallet N, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>758350</v>
+        <v>758253</v>
       </c>
       <c r="R12" t="n">
-        <v>7226181</v>
+        <v>7226123</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 53122-2024 artfynd.xlsx
+++ b/artfynd/A 53122-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747613</v>
+        <v>122747642</v>
       </c>
       <c r="B3" t="n">
-        <v>92268</v>
+        <v>90455</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>256703</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758391</v>
+        <v>758356</v>
       </c>
       <c r="R3" t="n">
-        <v>7226328</v>
+        <v>7226127</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747630</v>
+        <v>122747629</v>
       </c>
       <c r="B4" t="n">
-        <v>97325</v>
+        <v>92227</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758356</v>
+        <v>758350</v>
       </c>
       <c r="R4" t="n">
-        <v>7226177</v>
+        <v>7226181</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747611</v>
+        <v>122747626</v>
       </c>
       <c r="B5" t="n">
-        <v>92225</v>
+        <v>97325</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758277</v>
+        <v>758357</v>
       </c>
       <c r="R5" t="n">
-        <v>7226119</v>
+        <v>7226191</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747633</v>
+        <v>122747609</v>
       </c>
       <c r="B6" t="n">
-        <v>92233</v>
+        <v>89995</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet N, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>758361</v>
+        <v>758253</v>
       </c>
       <c r="R6" t="n">
-        <v>7226178</v>
+        <v>7226123</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747642</v>
+        <v>122747619</v>
       </c>
       <c r="B7" t="n">
-        <v>90455</v>
+        <v>89995</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>256703</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>758356</v>
+        <v>758431</v>
       </c>
       <c r="R7" t="n">
-        <v>7226127</v>
+        <v>7226257</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747606</v>
+        <v>122747630</v>
       </c>
       <c r="B8" t="n">
-        <v>90455</v>
+        <v>97325</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,34 +1327,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>256703</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>758247</v>
+        <v>758356</v>
       </c>
       <c r="R8" t="n">
-        <v>7226119</v>
+        <v>7226177</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747626</v>
+        <v>122747633</v>
       </c>
       <c r="B9" t="n">
-        <v>97325</v>
+        <v>92233</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>758357</v>
+        <v>758361</v>
       </c>
       <c r="R9" t="n">
-        <v>7226191</v>
+        <v>7226178</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747641</v>
+        <v>122747635</v>
       </c>
       <c r="B10" t="n">
-        <v>91706</v>
+        <v>92227</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,38 +1535,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1958</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>758366</v>
+        <v>758363</v>
       </c>
       <c r="R10" t="n">
-        <v>7226139</v>
+        <v>7226170</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747629</v>
+        <v>122747624</v>
       </c>
       <c r="B11" t="n">
         <v>92227</v>
@@ -1665,14 +1665,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758350</v>
+        <v>758400</v>
       </c>
       <c r="R11" t="n">
-        <v>7226181</v>
+        <v>7226209</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122747609</v>
+        <v>122747611</v>
       </c>
       <c r="B12" t="n">
-        <v>89995</v>
+        <v>92225</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,34 +1751,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åfallet N, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>758253</v>
+        <v>758277</v>
       </c>
       <c r="R12" t="n">
-        <v>7226123</v>
+        <v>7226119</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122747624</v>
+        <v>122747606</v>
       </c>
       <c r="B13" t="n">
-        <v>92227</v>
+        <v>90455</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,38 +1853,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>758400</v>
+        <v>758247</v>
       </c>
       <c r="R13" t="n">
-        <v>7226209</v>
+        <v>7226119</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122747619</v>
+        <v>122747639</v>
       </c>
       <c r="B14" t="n">
-        <v>89995</v>
+        <v>92233</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,38 +1959,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>758431</v>
+        <v>758361</v>
       </c>
       <c r="R14" t="n">
-        <v>7226257</v>
+        <v>7226146</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122747614</v>
+        <v>122747613</v>
       </c>
       <c r="B15" t="n">
-        <v>92225</v>
+        <v>92268</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,34 +2069,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>758432</v>
+        <v>758391</v>
       </c>
       <c r="R15" t="n">
-        <v>7226289</v>
+        <v>7226328</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747604</v>
+        <v>122747614</v>
       </c>
       <c r="B16" t="n">
-        <v>90455</v>
+        <v>92225</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,38 +2171,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>256703</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>758256</v>
+        <v>758432</v>
       </c>
       <c r="R16" t="n">
-        <v>7226053</v>
+        <v>7226289</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747635</v>
+        <v>122747604</v>
       </c>
       <c r="B17" t="n">
-        <v>92227</v>
+        <v>90455</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,38 +2277,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>758363</v>
+        <v>758256</v>
       </c>
       <c r="R17" t="n">
-        <v>7226170</v>
+        <v>7226053</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122747639</v>
+        <v>122747641</v>
       </c>
       <c r="B18" t="n">
-        <v>92233</v>
+        <v>91706</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,38 +2383,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>758361</v>
+        <v>758366</v>
       </c>
       <c r="R18" t="n">
-        <v>7226146</v>
+        <v>7226139</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 53122-2024 artfynd.xlsx
+++ b/artfynd/A 53122-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747638</v>
+        <v>122747642</v>
       </c>
       <c r="B2" t="n">
-        <v>91706</v>
+        <v>90455</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1958</v>
+        <v>256703</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gökberget V, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758363</v>
+        <v>758356</v>
       </c>
       <c r="R2" t="n">
-        <v>7226141</v>
+        <v>7226127</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747642</v>
+        <v>122747613</v>
       </c>
       <c r="B3" t="n">
-        <v>90455</v>
+        <v>92268</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>256703</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758356</v>
+        <v>758391</v>
       </c>
       <c r="R3" t="n">
-        <v>7226127</v>
+        <v>7226328</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747629</v>
+        <v>122747611</v>
       </c>
       <c r="B4" t="n">
-        <v>92227</v>
+        <v>92225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758350</v>
+        <v>758277</v>
       </c>
       <c r="R4" t="n">
-        <v>7226181</v>
+        <v>7226119</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747609</v>
+        <v>122747630</v>
       </c>
       <c r="B6" t="n">
-        <v>89995</v>
+        <v>97325</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åfallet N, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>758253</v>
+        <v>758356</v>
       </c>
       <c r="R6" t="n">
-        <v>7226123</v>
+        <v>7226177</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747619</v>
+        <v>122747624</v>
       </c>
       <c r="B7" t="n">
-        <v>89995</v>
+        <v>92227</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>758431</v>
+        <v>758400</v>
       </c>
       <c r="R7" t="n">
-        <v>7226257</v>
+        <v>7226209</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747630</v>
+        <v>122747633</v>
       </c>
       <c r="B8" t="n">
-        <v>97325</v>
+        <v>92233</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,34 +1327,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>758356</v>
+        <v>758361</v>
       </c>
       <c r="R8" t="n">
-        <v>7226177</v>
+        <v>7226178</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747633</v>
+        <v>122747635</v>
       </c>
       <c r="B9" t="n">
-        <v>92233</v>
+        <v>92227</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,38 +1429,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>758361</v>
+        <v>758363</v>
       </c>
       <c r="R9" t="n">
-        <v>7226178</v>
+        <v>7226170</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747635</v>
+        <v>122747629</v>
       </c>
       <c r="B10" t="n">
         <v>92227</v>
@@ -1559,14 +1559,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>758363</v>
+        <v>758350</v>
       </c>
       <c r="R10" t="n">
-        <v>7226170</v>
+        <v>7226181</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747624</v>
+        <v>122747639</v>
       </c>
       <c r="B11" t="n">
-        <v>92227</v>
+        <v>92233</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,38 +1641,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758400</v>
+        <v>758361</v>
       </c>
       <c r="R11" t="n">
-        <v>7226209</v>
+        <v>7226146</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122747611</v>
+        <v>122747614</v>
       </c>
       <c r="B12" t="n">
         <v>92225</v>
@@ -1771,14 +1771,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>758277</v>
+        <v>758432</v>
       </c>
       <c r="R12" t="n">
-        <v>7226119</v>
+        <v>7226289</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122747606</v>
+        <v>122747638</v>
       </c>
       <c r="B13" t="n">
-        <v>90455</v>
+        <v>91706</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,38 +1853,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>256703</v>
+        <v>1958</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Gökberget V, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>758247</v>
+        <v>758363</v>
       </c>
       <c r="R13" t="n">
-        <v>7226119</v>
+        <v>7226141</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122747639</v>
+        <v>122747619</v>
       </c>
       <c r="B14" t="n">
-        <v>92233</v>
+        <v>89995</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,38 +1959,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>758361</v>
+        <v>758431</v>
       </c>
       <c r="R14" t="n">
-        <v>7226146</v>
+        <v>7226257</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122747613</v>
+        <v>122747609</v>
       </c>
       <c r="B15" t="n">
-        <v>92268</v>
+        <v>89995</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,34 +2069,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Åfallet N, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>758391</v>
+        <v>758253</v>
       </c>
       <c r="R15" t="n">
-        <v>7226328</v>
+        <v>7226123</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747614</v>
+        <v>122747641</v>
       </c>
       <c r="B16" t="n">
-        <v>92225</v>
+        <v>91706</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,38 +2171,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>1958</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>758432</v>
+        <v>758366</v>
       </c>
       <c r="R16" t="n">
-        <v>7226289</v>
+        <v>7226139</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122747641</v>
+        <v>122747606</v>
       </c>
       <c r="B18" t="n">
-        <v>91706</v>
+        <v>90455</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,38 +2383,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1958</v>
+        <v>256703</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>758366</v>
+        <v>758247</v>
       </c>
       <c r="R18" t="n">
-        <v>7226139</v>
+        <v>7226119</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 53122-2024 artfynd.xlsx
+++ b/artfynd/A 53122-2024 artfynd.xlsx
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747641</v>
+        <v>122747604</v>
       </c>
       <c r="B16" t="n">
-        <v>91706</v>
+        <v>90455</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,38 +2171,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1958</v>
+        <v>256703</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>758366</v>
+        <v>758256</v>
       </c>
       <c r="R16" t="n">
-        <v>7226139</v>
+        <v>7226053</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747604</v>
+        <v>122747641</v>
       </c>
       <c r="B17" t="n">
-        <v>90455</v>
+        <v>91706</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,38 +2277,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>256703</v>
+        <v>1958</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>758256</v>
+        <v>758366</v>
       </c>
       <c r="R17" t="n">
-        <v>7226053</v>
+        <v>7226139</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 53122-2024 artfynd.xlsx
+++ b/artfynd/A 53122-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747642</v>
+        <v>122747639</v>
       </c>
       <c r="B2" t="n">
-        <v>90455</v>
+        <v>92236</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758356</v>
+        <v>758361</v>
       </c>
       <c r="R2" t="n">
-        <v>7226127</v>
+        <v>7226146</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747613</v>
+        <v>122747619</v>
       </c>
       <c r="B3" t="n">
-        <v>92268</v>
+        <v>89998</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758391</v>
+        <v>758431</v>
       </c>
       <c r="R3" t="n">
-        <v>7226328</v>
+        <v>7226257</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>122747611</v>
       </c>
       <c r="B4" t="n">
-        <v>92225</v>
+        <v>92228</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>122747626</v>
       </c>
       <c r="B5" t="n">
-        <v>97325</v>
+        <v>97328</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747630</v>
+        <v>122747604</v>
       </c>
       <c r="B6" t="n">
-        <v>97325</v>
+        <v>90458</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,34 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>256703</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>758356</v>
+        <v>758256</v>
       </c>
       <c r="R6" t="n">
-        <v>7226177</v>
+        <v>7226053</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747624</v>
+        <v>122747641</v>
       </c>
       <c r="B7" t="n">
-        <v>92227</v>
+        <v>91709</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>758400</v>
+        <v>758366</v>
       </c>
       <c r="R7" t="n">
-        <v>7226209</v>
+        <v>7226139</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747633</v>
+        <v>122747629</v>
       </c>
       <c r="B8" t="n">
-        <v>92233</v>
+        <v>92230</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>758361</v>
+        <v>758350</v>
       </c>
       <c r="R8" t="n">
-        <v>7226178</v>
+        <v>7226181</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747635</v>
+        <v>122747642</v>
       </c>
       <c r="B9" t="n">
-        <v>92227</v>
+        <v>90458</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,38 +1429,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>758363</v>
+        <v>758356</v>
       </c>
       <c r="R9" t="n">
-        <v>7226170</v>
+        <v>7226127</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747629</v>
+        <v>122747613</v>
       </c>
       <c r="B10" t="n">
-        <v>92227</v>
+        <v>92271</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,34 +1539,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>758350</v>
+        <v>758391</v>
       </c>
       <c r="R10" t="n">
-        <v>7226181</v>
+        <v>7226328</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747639</v>
+        <v>122747606</v>
       </c>
       <c r="B11" t="n">
-        <v>92233</v>
+        <v>90458</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,34 +1645,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758361</v>
+        <v>758247</v>
       </c>
       <c r="R11" t="n">
-        <v>7226146</v>
+        <v>7226119</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122747614</v>
+        <v>122747635</v>
       </c>
       <c r="B12" t="n">
-        <v>92225</v>
+        <v>92230</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,34 +1751,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>758432</v>
+        <v>758363</v>
       </c>
       <c r="R12" t="n">
-        <v>7226289</v>
+        <v>7226170</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122747638</v>
+        <v>122747614</v>
       </c>
       <c r="B13" t="n">
-        <v>91706</v>
+        <v>92228</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,38 +1853,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1958</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gökberget V, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>758363</v>
+        <v>758432</v>
       </c>
       <c r="R13" t="n">
-        <v>7226141</v>
+        <v>7226289</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122747619</v>
+        <v>122747609</v>
       </c>
       <c r="B14" t="n">
-        <v>89995</v>
+        <v>89998</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,14 +1983,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Åfallet N, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>758431</v>
+        <v>758253</v>
       </c>
       <c r="R14" t="n">
-        <v>7226257</v>
+        <v>7226123</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122747609</v>
+        <v>122747633</v>
       </c>
       <c r="B15" t="n">
-        <v>89995</v>
+        <v>92236</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,38 +2065,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Åfallet N, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>758253</v>
+        <v>758361</v>
       </c>
       <c r="R15" t="n">
-        <v>7226123</v>
+        <v>7226178</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747604</v>
+        <v>122747624</v>
       </c>
       <c r="B16" t="n">
-        <v>90455</v>
+        <v>92230</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,38 +2171,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>256703</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>758256</v>
+        <v>758400</v>
       </c>
       <c r="R16" t="n">
-        <v>7226053</v>
+        <v>7226209</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747641</v>
+        <v>122747638</v>
       </c>
       <c r="B17" t="n">
-        <v>91706</v>
+        <v>91709</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,14 +2301,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Gökberget V, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>758366</v>
+        <v>758363</v>
       </c>
       <c r="R17" t="n">
-        <v>7226139</v>
+        <v>7226141</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122747606</v>
+        <v>122747630</v>
       </c>
       <c r="B18" t="n">
-        <v>90455</v>
+        <v>97328</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,34 +2387,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>256703</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>758247</v>
+        <v>758356</v>
       </c>
       <c r="R18" t="n">
-        <v>7226119</v>
+        <v>7226177</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 53122-2024 artfynd.xlsx
+++ b/artfynd/A 53122-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747639</v>
+        <v>122747619</v>
       </c>
       <c r="B2" t="n">
-        <v>92236</v>
+        <v>90000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758361</v>
+        <v>758431</v>
       </c>
       <c r="R2" t="n">
-        <v>7226146</v>
+        <v>7226257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747619</v>
+        <v>122747606</v>
       </c>
       <c r="B3" t="n">
-        <v>89998</v>
+        <v>90460</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>256703</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758431</v>
+        <v>758247</v>
       </c>
       <c r="R3" t="n">
-        <v>7226257</v>
+        <v>7226119</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747611</v>
+        <v>122747614</v>
       </c>
       <c r="B4" t="n">
-        <v>92228</v>
+        <v>92230</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,14 +923,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758277</v>
+        <v>758432</v>
       </c>
       <c r="R4" t="n">
-        <v>7226119</v>
+        <v>7226289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747626</v>
+        <v>122747635</v>
       </c>
       <c r="B5" t="n">
-        <v>97328</v>
+        <v>92232</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758357</v>
+        <v>758363</v>
       </c>
       <c r="R5" t="n">
-        <v>7226191</v>
+        <v>7226170</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747604</v>
+        <v>122747609</v>
       </c>
       <c r="B6" t="n">
-        <v>90458</v>
+        <v>90000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>256703</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Åfallet N, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>758256</v>
+        <v>758253</v>
       </c>
       <c r="R6" t="n">
-        <v>7226053</v>
+        <v>7226123</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747641</v>
+        <v>122747630</v>
       </c>
       <c r="B7" t="n">
-        <v>91709</v>
+        <v>97330</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1958</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>758366</v>
+        <v>758356</v>
       </c>
       <c r="R7" t="n">
-        <v>7226139</v>
+        <v>7226177</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747629</v>
+        <v>122747604</v>
       </c>
       <c r="B8" t="n">
-        <v>92230</v>
+        <v>90460</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Norderåsen V, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>758350</v>
+        <v>758256</v>
       </c>
       <c r="R8" t="n">
-        <v>7226181</v>
+        <v>7226053</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747642</v>
+        <v>122747629</v>
       </c>
       <c r="B9" t="n">
-        <v>90458</v>
+        <v>92232</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,38 +1429,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>256703</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>758356</v>
+        <v>758350</v>
       </c>
       <c r="R9" t="n">
-        <v>7226127</v>
+        <v>7226181</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747613</v>
+        <v>122747624</v>
       </c>
       <c r="B10" t="n">
-        <v>92271</v>
+        <v>92232</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,34 +1539,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>758391</v>
+        <v>758400</v>
       </c>
       <c r="R10" t="n">
-        <v>7226328</v>
+        <v>7226209</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122747606</v>
+        <v>122747642</v>
       </c>
       <c r="B11" t="n">
-        <v>90458</v>
+        <v>90460</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,14 +1665,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Norderåsen V, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758247</v>
+        <v>758356</v>
       </c>
       <c r="R11" t="n">
-        <v>7226119</v>
+        <v>7226127</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122747635</v>
+        <v>122747641</v>
       </c>
       <c r="B12" t="n">
-        <v>92230</v>
+        <v>91711</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,38 +1747,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Åfallet NÖ, Vb</t>
+          <t>Lillåstj. SÖ, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>758363</v>
+        <v>758366</v>
       </c>
       <c r="R12" t="n">
-        <v>7226170</v>
+        <v>7226139</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122747614</v>
+        <v>122747626</v>
       </c>
       <c r="B13" t="n">
-        <v>92228</v>
+        <v>97330</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,25 +1853,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>758432</v>
+        <v>758357</v>
       </c>
       <c r="R13" t="n">
-        <v>7226289</v>
+        <v>7226191</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1947,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122747609</v>
+        <v>122747613</v>
       </c>
       <c r="B14" t="n">
-        <v>89998</v>
+        <v>92273</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,34 +1963,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Åfallet N, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>758253</v>
+        <v>758391</v>
       </c>
       <c r="R14" t="n">
-        <v>7226123</v>
+        <v>7226328</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2053,10 +2053,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122747633</v>
+        <v>122747611</v>
       </c>
       <c r="B15" t="n">
-        <v>92236</v>
+        <v>92230</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2065,38 +2065,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>758361</v>
+        <v>758277</v>
       </c>
       <c r="R15" t="n">
-        <v>7226178</v>
+        <v>7226119</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2159,10 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122747624</v>
+        <v>122747638</v>
       </c>
       <c r="B16" t="n">
-        <v>92230</v>
+        <v>91711</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,38 +2171,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Renskinns- NV, Vb</t>
+          <t>Gökberget V, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>758400</v>
+        <v>758363</v>
       </c>
       <c r="R16" t="n">
-        <v>7226209</v>
+        <v>7226141</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2265,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122747638</v>
+        <v>122747639</v>
       </c>
       <c r="B17" t="n">
-        <v>91709</v>
+        <v>92238</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2277,38 +2277,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gökberget V, Vb</t>
+          <t>Åfallet NÖ, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>758363</v>
+        <v>758361</v>
       </c>
       <c r="R17" t="n">
-        <v>7226141</v>
+        <v>7226146</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2371,10 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122747630</v>
+        <v>122747633</v>
       </c>
       <c r="B18" t="n">
-        <v>97328</v>
+        <v>92238</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2387,34 +2387,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillåstj. SÖ, Vb</t>
+          <t>Renskinns- NV, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>758356</v>
+        <v>758361</v>
       </c>
       <c r="R18" t="n">
-        <v>7226177</v>
+        <v>7226178</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg, Helene Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
